--- a/从零开始学Slots/从零开始学Slots-01-基础篇-基础构成.xlsx
+++ b/从零开始学Slots/从零开始学Slots-01-基础篇-基础构成.xlsx
@@ -12934,6 +12934,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:AO296" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -15167,5 +15170,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M158" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-01-基础篇-基础构成.xlsx
+++ b/从零开始学Slots/从零开始学Slots-01-基础篇-基础构成.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="数据配表的实现" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="415">
   <si>
     <r>
       <rPr>
@@ -10898,7 +10898,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -10961,6 +10961,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -12068,13 +12076,13 @@
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="21" t="s">
-        <v>85</v>
+      <c r="A101" s="33">
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="21" t="s">
-        <v>86</v>
+      <c r="A102" s="33">
+        <v>40</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -13405,8 +13413,8 @@
       <c r="A34" s="1">
         <v>9</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>251</v>
+      <c r="B34" s="34">
+        <v>10</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>250</v>
@@ -13425,8 +13433,8 @@
       <c r="A35" s="1">
         <v>10</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>251</v>
+      <c r="B35" s="34">
+        <v>10</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>250</v>
@@ -13445,8 +13453,8 @@
       <c r="A36" s="1">
         <v>11</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>251</v>
+      <c r="B36" s="34">
+        <v>10</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>250</v>
@@ -13465,160 +13473,160 @@
       <c r="A37" s="1">
         <v>12</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>251</v>
+      <c r="B37" s="34">
+        <v>10</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>251</v>
+      <c r="D37" s="34">
+        <v>10</v>
+      </c>
+      <c r="E37" s="34">
+        <v>10</v>
+      </c>
+      <c r="F37" s="34">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>13</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>251</v>
+      <c r="B38" s="34">
+        <v>10</v>
+      </c>
+      <c r="C38" s="34">
+        <v>10</v>
+      </c>
+      <c r="D38" s="34">
+        <v>10</v>
+      </c>
+      <c r="E38" s="34">
+        <v>10</v>
+      </c>
+      <c r="F38" s="34">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>14</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>251</v>
+      <c r="B39" s="34">
+        <v>9</v>
+      </c>
+      <c r="C39" s="34">
+        <v>10</v>
+      </c>
+      <c r="D39" s="34">
+        <v>10</v>
+      </c>
+      <c r="E39" s="34">
+        <v>10</v>
+      </c>
+      <c r="F39" s="34">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>15</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>251</v>
+      <c r="B40" s="34">
+        <v>9</v>
+      </c>
+      <c r="C40" s="34">
+        <v>10</v>
+      </c>
+      <c r="D40" s="34">
+        <v>10</v>
+      </c>
+      <c r="E40" s="34">
+        <v>10</v>
+      </c>
+      <c r="F40" s="34">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>16</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>252</v>
+      <c r="B41" s="34">
+        <v>9</v>
+      </c>
+      <c r="C41" s="34">
+        <v>9</v>
+      </c>
+      <c r="D41" s="34">
+        <v>9</v>
+      </c>
+      <c r="E41" s="34">
+        <v>9</v>
+      </c>
+      <c r="F41" s="34">
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>17</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>252</v>
+      <c r="B42" s="34">
+        <v>9</v>
+      </c>
+      <c r="C42" s="34">
+        <v>9</v>
+      </c>
+      <c r="D42" s="34">
+        <v>9</v>
+      </c>
+      <c r="E42" s="34">
+        <v>9</v>
+      </c>
+      <c r="F42" s="34">
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>18</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>252</v>
+      <c r="B43" s="34">
+        <v>9</v>
+      </c>
+      <c r="C43" s="34">
+        <v>9</v>
+      </c>
+      <c r="D43" s="34">
+        <v>9</v>
+      </c>
+      <c r="E43" s="34">
+        <v>9</v>
+      </c>
+      <c r="F43" s="34">
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>19</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>252</v>
+      <c r="B44" s="34">
+        <v>9</v>
+      </c>
+      <c r="C44" s="34">
+        <v>9</v>
+      </c>
+      <c r="D44" s="34">
+        <v>9</v>
+      </c>
+      <c r="E44" s="34">
+        <v>9</v>
+      </c>
+      <c r="F44" s="34">
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -13802,8 +13810,8 @@
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="8" t="s">
-        <v>251</v>
+      <c r="A53" s="35">
+        <v>10</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>259</v>
@@ -13833,8 +13841,8 @@
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="8" t="s">
-        <v>252</v>
+      <c r="A54" s="35">
+        <v>9</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>259</v>
@@ -13969,14 +13977,14 @@
       <c r="A60" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B60" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>270</v>
+      <c r="B60" s="36">
+        <v>3</v>
+      </c>
+      <c r="C60" s="36">
+        <v>4</v>
+      </c>
+      <c r="D60" s="36">
+        <v>5</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>271</v>
@@ -14051,8 +14059,8 @@
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="8" t="s">
-        <v>251</v>
+      <c r="A64" s="35">
+        <v>10</v>
       </c>
       <c r="B64" s="6">
         <v>5</v>
@@ -14067,13 +14075,13 @@
         <f>IF(AND(B64&lt;C64,C64&lt;D64),"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F64" s="8" t="s">
-        <v>275</v>
+      <c r="F64" s="35">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="8" t="s">
-        <v>252</v>
+      <c r="A65" s="35">
+        <v>9</v>
       </c>
       <c r="B65" s="6">
         <v>5</v>
@@ -14088,8 +14096,8 @@
         <f>IF(AND(B65&lt;C65,C65&lt;D65),"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="F65" s="8" t="s">
-        <v>276</v>
+      <c r="F65" s="35">
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -14333,8 +14341,8 @@
       <c r="F80" s="15"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="8" t="s">
-        <v>251</v>
+      <c r="A81" s="35">
+        <v>10</v>
       </c>
       <c r="B81" s="10" t="s">
         <v>290</v>
@@ -14347,8 +14355,8 @@
       <c r="F81" s="15"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="8" t="s">
-        <v>252</v>
+      <c r="A82" s="35">
+        <v>9</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>290</v>
